--- a/moodys_datahub/data/data_products.xlsx
+++ b/moodys_datahub/data/data_products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/kgp_lib_cbs_dk/Documents/Desktop/moody-s_datahub/moodys_datahub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="11_4B0D37945B70D6289F9A3B11595ED87656CCA927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E81CF769-7A8D-4472-BC6A-762F13207DB6}"/>
+  <xr:revisionPtr revIDLastSave="174" documentId="11_4B0D37945B70D6289F9A3B11595ED87656CCA927" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{072A19C1-F2A3-4D82-B17B-9BB0844E3505}"/>
   <bookViews>
-    <workbookView xWindow="12045" yWindow="4530" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="187">
   <si>
     <t>Data Product</t>
   </si>
@@ -572,6 +572,18 @@
   </si>
   <si>
     <t>6BNu42CgRuSBOqFmMmUAdw</t>
+  </si>
+  <si>
+    <t>Probability of Default</t>
+  </si>
+  <si>
+    <t>probability_of_default_by_moodys_analytics</t>
+  </si>
+  <si>
+    <t>REiuMSZWT5GJQgIZIQmD6A</t>
+  </si>
+  <si>
+    <t>IlbXwno7RM6H7et71MD3Uw</t>
   </si>
 </sst>
 </file>
@@ -953,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="47.42578125" customWidth="1"/>
@@ -6075,6 +6087,40 @@
         <v>174</v>
       </c>
     </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="B302" t="s">
+        <v>183</v>
+      </c>
+      <c r="C302" t="s">
+        <v>184</v>
+      </c>
+      <c r="D302" t="s">
+        <v>185</v>
+      </c>
+      <c r="E302" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="B303" t="s">
+        <v>183</v>
+      </c>
+      <c r="C303" t="s">
+        <v>184</v>
+      </c>
+      <c r="D303" t="s">
+        <v>186</v>
+      </c>
+      <c r="E303" t="s">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E301" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E301">
